--- a/WhatsappBulkInterview/kandidat.xlsx
+++ b/WhatsappBulkInterview/kandidat.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>nama_kandidat</t>
   </si>
@@ -27,13 +27,34 @@
     <t>posisi</t>
   </si>
   <si>
-    <t xml:space="preserve">Andi Saputra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Spesialis Search Engine Optimization (SEO) via Glints</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Siti Aisyah</t>
+    <t>Jam</t>
+  </si>
+  <si>
+    <t>StatusInterview</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putri Septianingrum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search Engine Optimization (SEO) via Glints</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putri Hesti Lestari</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adelia Vita</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ade Krisna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lulu Luqyana Najmi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Siti Adisya Kirana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arinda Cahyani Azizah</t>
   </si>
 </sst>
 </file>
@@ -68,9 +89,15 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,8 +597,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col bestFit="1" min="2" max="2" style="0" width="17.00390625"/>
-    <col bestFit="1" min="3" max="3" width="17.76171875"/>
+    <col customWidth="1" min="1" max="1" width="19.28125"/>
+    <col customWidth="1" min="2" max="2" style="0" width="38.00390625"/>
+    <col bestFit="1" min="3" max="3" width="51.76171875"/>
+    <col bestFit="1" min="4" max="4" width="4.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -584,28 +613,96 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" ht="14.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="1">
-        <v>6281286359772</v>
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3">
+        <v>6285591211482</v>
       </c>
       <c r="C2" t="s">
-        <v>4</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D2" s="4"/>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1">
-        <v>6285156137026</v>
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>6288902808637</v>
       </c>
       <c r="C3" t="s">
-        <v>4</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" ht="14.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
+        <v>6282114874308</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" ht="14.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>628977226429</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4"/>
+    </row>
+    <row r="6" ht="14.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>6282130561174</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" ht="14.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>6285773004721</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" ht="14.25">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>6283116841592</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" ht="14.25">
+      <c r="A9"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>

--- a/WhatsappBulkInterview/kandidat.xlsx
+++ b/WhatsappBulkInterview/kandidat.xlsx
@@ -27,7 +27,7 @@
     <t>posisi</t>
   </si>
   <si>
-    <t>Jam</t>
+    <t>jam</t>
   </si>
   <si>
     <t>StatusInterview</t>
@@ -89,12 +89,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="20" xfId="0" applyNumberFormat="1"/>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -598,9 +597,10 @@
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="19.28125"/>
-    <col customWidth="1" min="2" max="2" style="0" width="38.00390625"/>
+    <col bestFit="1" customWidth="1" min="2" max="2" style="0" width="11.76171875"/>
     <col bestFit="1" min="3" max="3" width="51.76171875"/>
-    <col bestFit="1" min="4" max="4" width="4.140625"/>
+    <col bestFit="1" min="4" max="4" width="5.47265625"/>
+    <col bestFit="1" min="5" max="5" width="14.23046875"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25">
@@ -624,25 +624,29 @@
       <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="2">
         <v>6285591211482</v>
       </c>
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="3">
+        <v>0.41666666666666669</v>
+      </c>
     </row>
     <row r="3" ht="14.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="2">
         <v>6288902808637</v>
       </c>
       <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3">
+        <v>0.41666666666666669</v>
+      </c>
     </row>
     <row r="4" ht="14.25">
       <c r="A4" t="s">
@@ -654,7 +658,9 @@
       <c r="C4" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3">
+        <v>0.41666666666666669</v>
+      </c>
     </row>
     <row r="5" ht="14.25">
       <c r="A5" t="s">
@@ -666,7 +672,9 @@
       <c r="C5" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4"/>
+      <c r="D5" s="3">
+        <v>0.41666666666666669</v>
+      </c>
     </row>
     <row r="6" ht="14.25">
       <c r="A6" t="s">
@@ -675,8 +683,11 @@
       <c r="B6">
         <v>6282130561174</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="7" ht="14.25">
@@ -686,8 +697,11 @@
       <c r="B7">
         <v>6285773004721</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>6</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0.45833333333333331</v>
       </c>
     </row>
     <row r="8" ht="14.25">
@@ -697,12 +711,12 @@
       <c r="B8">
         <v>6283116841592</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="9" ht="14.25">
-      <c r="A9"/>
+      <c r="D8" s="3">
+        <v>0.45833333333333331</v>
+      </c>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
